--- a/output/2026-09-04_23_Italia_Calabria_Cleaning.xlsx
+++ b/output/2026-09-04_23_Italia_Calabria_Cleaning.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centro assistenza autorizzato Kärcher; assemblaggio, vendita e manutenzione di idropulitrici e macchine per pulizia ad alta pressione. Sede a Montalto Uffugo (CS). Verificato via misterimprese.it e reportaziende.it.</t>
+          <t>Centro assistenza autorizzato Kärcher; assemblaggio, vendita e manutenzione di idropulitrici e macchine per pulizia ad alta pressione. Sede a Montalto Uffugo (CS). Verificato via misterimprese.it e reportaziende.it. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -620,7 +620,6 @@
           <t>0984 393839</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Catena di ingrosso/dettaglio 'Pianeta Pulito' (marchio Gruppo VéGé) per articoli di pulizia, igiene e monouso, con 5 punti vendita in provincia di Cosenza. Email generica non reperita.</t>
@@ -742,7 +741,6 @@
           <t>0965 642171</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Produzione e commercializzazione di detergenti/prodotti chimici per pulizia industriale e civile da oltre 35 anni; opera anche in disinfestazione/derattizzazione. Email generica non reperita.</t>
@@ -822,7 +820,6 @@
           <t>0965 324057</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>E-commerce/negozio con sezione dedicata a idropulitrici e attrezzature per pulizia esterna/giardino. Sede a Reggio Calabria (RC). Email generica non reperita.</t>
@@ -855,8 +852,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Forniture alberghiere/Ho.Re.Ca. con linea dedicata 'cleaning' per hotel, ristoranti e b&amp;b. Sede a Marina di Gioiosa Jonica (RC). Telefono ed email non reperiti/verificabili.</t>
@@ -894,7 +889,6 @@
           <t>0964 388297</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Utensileria per officine con linea dedicata a compressori e idropulitrici professionali, oltre ad attrezzature antinfortunistica. Sede a Siderno (RC). Email generica non reperita.</t>
@@ -954,7 +948,6 @@
           <t>F.M. Chimica S.r.l.s.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Crotone (KR)</t>
@@ -970,7 +963,6 @@
           <t>0962 930406</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Produzione e commercializzazione di detergenti liquidi professionali dal 2011, con laboratorio R&amp;D interno. Sede a Crotone (KR). Sito web ed email non reperiti.</t>
@@ -988,7 +980,6 @@
           <t>F.A.P. S.a.s. di Vrenna Giovanni e C.</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Crotone (KR)</t>
@@ -1004,7 +995,6 @@
           <t>0962 62369</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Prodotti chimici per la pulizia della casa, decapanti e abrasivi chimici (listato su Europages). Sede a Crotone (KR). Sito web ed email non reperiti.</t>

--- a/output/2026-09-04_23_Italia_Calabria_Cleaning.xlsx
+++ b/output/2026-09-04_23_Italia_Calabria_Cleaning.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
